--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>127085015</v>
       </c>
       <c r="B6" t="n">
-        <v>79059</v>
+        <v>79090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>127085043</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>127084982</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127084596</v>
       </c>
       <c r="B11" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>127084790</v>
       </c>
       <c r="B12" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>127085015</v>
       </c>
       <c r="B6" t="n">
-        <v>79090</v>
+        <v>79093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127084079</v>
+        <v>127084140</v>
       </c>
       <c r="B7" t="n">
         <v>57657</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>369379</v>
+        <v>369501</v>
       </c>
       <c r="R7" t="n">
-        <v>6942401</v>
+        <v>6942463</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127084140</v>
+        <v>127084079</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369501</v>
+        <v>369379</v>
       </c>
       <c r="R8" t="n">
-        <v>6942463</v>
+        <v>6942401</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1436,7 +1436,7 @@
         <v>127085043</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>127084982</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127084596</v>
       </c>
       <c r="B11" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>127084790</v>
       </c>
       <c r="B12" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127084140</v>
+        <v>127084079</v>
       </c>
       <c r="B7" t="n">
         <v>57657</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>369501</v>
+        <v>369379</v>
       </c>
       <c r="R7" t="n">
-        <v>6942463</v>
+        <v>6942401</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127084079</v>
+        <v>127084140</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369379</v>
+        <v>369501</v>
       </c>
       <c r="R8" t="n">
-        <v>6942401</v>
+        <v>6942463</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>127085015</v>
       </c>
       <c r="B6" t="n">
-        <v>79093</v>
+        <v>79097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127084079</v>
+        <v>127084140</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>369379</v>
+        <v>369501</v>
       </c>
       <c r="R7" t="n">
-        <v>6942401</v>
+        <v>6942463</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127084140</v>
+        <v>127084079</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369501</v>
+        <v>369379</v>
       </c>
       <c r="R8" t="n">
-        <v>6942463</v>
+        <v>6942401</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1436,7 +1436,7 @@
         <v>127085043</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>127084982</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127084596</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>127084790</v>
       </c>
       <c r="B12" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>127085015</v>
       </c>
       <c r="B6" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>127084140</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>127084079</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>127085043</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>127084982</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127084596</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>127084790</v>
       </c>
       <c r="B12" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>127085015</v>
       </c>
       <c r="B6" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127084140</v>
+        <v>127084079</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>369501</v>
+        <v>369379</v>
       </c>
       <c r="R7" t="n">
-        <v>6942463</v>
+        <v>6942401</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127084079</v>
+        <v>127084140</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369379</v>
+        <v>369501</v>
       </c>
       <c r="R8" t="n">
-        <v>6942401</v>
+        <v>6942463</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1436,7 +1436,7 @@
         <v>127085043</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>127084982</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127084596</v>
       </c>
       <c r="B11" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>127084790</v>
       </c>
       <c r="B12" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>127085015</v>
       </c>
       <c r="B6" t="n">
-        <v>79102</v>
+        <v>79090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>127084079</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>127084140</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>127085043</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>127084982</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127084596</v>
       </c>
       <c r="B11" t="n">
-        <v>79612</v>
+        <v>79600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>127084790</v>
       </c>
       <c r="B12" t="n">
-        <v>80162</v>
+        <v>80150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>127085015</v>
       </c>
       <c r="B6" t="n">
-        <v>79090</v>
+        <v>79102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>127084079</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>127084140</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>127085043</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>127084982</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127084596</v>
       </c>
       <c r="B11" t="n">
-        <v>79600</v>
+        <v>79612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>127084790</v>
       </c>
       <c r="B12" t="n">
-        <v>80150</v>
+        <v>80162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107587963</v>
+        <v>127085015</v>
       </c>
       <c r="B2" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>967</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>369327.9927500483</v>
+        <v>369697</v>
       </c>
       <c r="R2" t="n">
-        <v>6942222.52054303</v>
+        <v>6942415</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107588177</v>
+        <v>107587963</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>369442.0973487879</v>
+        <v>369328</v>
       </c>
       <c r="R3" t="n">
-        <v>6942140.996346758</v>
+        <v>6942223</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +841,9 @@
           <t>2023-03-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107588863</v>
+        <v>107717160</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,40 +881,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>369335.3602409881</v>
+        <v>369299</v>
       </c>
       <c r="R4" t="n">
-        <v>6942210.238108792</v>
+        <v>6942148</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,22 +936,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,16 +971,11 @@
         <v>107716668</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1060,10 +1004,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>369312.6556980122</v>
+        <v>369312</v>
       </c>
       <c r="R5" t="n">
-        <v>6942266.941466479</v>
+        <v>6942267</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,19 +1037,9 @@
           <t>2023-03-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,32 +1066,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127085015</v>
+        <v>127084982</v>
       </c>
       <c r="B6" t="n">
-        <v>79102</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1101,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369697</v>
+        <v>369676</v>
       </c>
       <c r="R6" t="n">
-        <v>6942415</v>
+        <v>6942420</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,53 +1163,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127084079</v>
+        <v>127085043</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>369379</v>
+        <v>369695</v>
       </c>
       <c r="R7" t="n">
-        <v>6942401</v>
+        <v>6942405</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,53 +1260,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127084140</v>
+        <v>127084790</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>80468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369501</v>
+        <v>369538</v>
       </c>
       <c r="R8" t="n">
-        <v>6942463</v>
+        <v>6942312</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,10 +1357,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127085043</v>
+        <v>96500656</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,37 +1368,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>369695</v>
+        <v>369367</v>
       </c>
       <c r="R9" t="n">
-        <v>6942405</v>
+        <v>6942422</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,12 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127084982</v>
+        <v>107588863</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,37 +1472,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Abborrtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>369676</v>
+        <v>369335</v>
       </c>
       <c r="R10" t="n">
-        <v>6942420</v>
+        <v>6942210</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1595,12 +1532,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127084596</v>
+        <v>127084079</v>
       </c>
       <c r="B11" t="n">
-        <v>79612</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,37 +1575,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>369703</v>
+        <v>369379</v>
       </c>
       <c r="R11" t="n">
-        <v>6942327</v>
+        <v>6942401</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1724,48 +1666,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127084790</v>
+        <v>127084140</v>
       </c>
       <c r="B12" t="n">
-        <v>80162</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>369538</v>
+        <v>369501</v>
       </c>
       <c r="R12" t="n">
-        <v>6942312</v>
+        <v>6942463</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1818,6 +1765,401 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127084528</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>369731</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6942252</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>107588177</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>369443</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6942141</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-03-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-03-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>107717192</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>369299</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6942148</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127084596</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>369703</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6942327</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36522-2025 artfynd.xlsx
+++ b/artfynd/A 36522-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085015</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107587963</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107717160</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1063,6 +1083,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107716668</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1160,6 +1185,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127084982</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1257,6 +1287,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127085043</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1354,6 +1389,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127084790</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96500656</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107588863</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127084079</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1765,6 +1820,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127084140</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1867,6 +1927,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127084528</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107588177</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2063,6 +2133,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107717192</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2160,8 +2235,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127084596</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>